--- a/_sync/HackMD同步對照表.xlsx
+++ b/_sync/HackMD同步對照表.xlsx
@@ -5116,11 +5116,7 @@
           <t>FANFIC/Homestuck/03_VrisTav｜練筆.md</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F133" s="6" t="n"/>
       <c r="G133" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SylfgfzPzl</t>
@@ -5153,11 +5149,7 @@
           <t>FANFIC/Homestuck/14_VrisTav｜Nonsense.md</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F134" s="6" t="n"/>
       <c r="G134" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SyafxMzDMe</t>
@@ -5190,11 +5182,7 @@
           <t>FANFIC/Homestuck/04_KarTez｜練筆.md</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F135" s="6" t="n"/>
       <c r="G135" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJbflGfDGe</t>
@@ -5227,11 +5215,7 @@
           <t>FANFIC/Homestuck/05_KarTez｜盲.md</t>
         </is>
       </c>
-      <c r="F136" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F136" s="6" t="n"/>
       <c r="G136" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ByfzgzGvze</t>
@@ -5264,11 +5248,7 @@
           <t>FANFIC/Homestuck/13_KarTez｜孤寂行星.md</t>
         </is>
       </c>
-      <c r="F137" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F137" s="6" t="n"/>
       <c r="G137" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Hy2zxMGPGl</t>
@@ -5301,11 +5281,7 @@
           <t>FANFIC/Homestuck/06_TezKar｜髮夾.md</t>
         </is>
       </c>
-      <c r="F138" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F138" s="6" t="n"/>
       <c r="G138" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJNfxGzwMl</t>
@@ -5338,11 +5314,7 @@
           <t>FANFIC/Homestuck/07_TezKar｜糖果.md</t>
         </is>
       </c>
-      <c r="F139" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F139" s="6" t="n"/>
       <c r="G139" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HkSzlfGDfg</t>
@@ -5375,11 +5347,7 @@
           <t>FANFIC/Homestuck/09_TezKar｜驟高.md</t>
         </is>
       </c>
-      <c r="F140" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F140" s="6" t="n"/>
       <c r="G140" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJwMefMPzl</t>
@@ -5412,11 +5380,7 @@
           <t>FANFIC/Homestuck/16_TezKar｜非自願觀賞.md</t>
         </is>
       </c>
-      <c r="F141" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F141" s="6" t="n"/>
       <c r="G141" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HklXgffPMe</t>
@@ -5449,11 +5413,7 @@
           <t>FANFIC/Homestuck/11_SolEri｜角噗之後.md</t>
         </is>
       </c>
-      <c r="F142" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F142" s="6" t="n"/>
       <c r="G142" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkFfezMwzl</t>
@@ -5486,11 +5446,7 @@
           <t>FANFIC/Homestuck/01_GamKar｜練筆.md</t>
         </is>
       </c>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F143" s="6" t="n"/>
       <c r="G143" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryaWxffvGg</t>
@@ -5523,11 +5479,7 @@
           <t>FANFIC/Homestuck/15_Kanaya+KarTez｜調解.md</t>
         </is>
       </c>
-      <c r="F144" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F144" s="6" t="n"/>
       <c r="G144" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1AGeGzDMg</t>
@@ -5560,11 +5512,7 @@
           <t>FANFIC/Homestuck/19_Meenah×Aranea｜寂寞路上是否有妳.md</t>
         </is>
       </c>
-      <c r="F145" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F145" s="6" t="n"/>
       <c r="G145" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1V7lGzDGg</t>
@@ -5597,11 +5545,7 @@
           <t>FANFIC/K/01_伏八｜隨筆.md</t>
         </is>
       </c>
-      <c r="F146" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F146" s="6" t="n"/>
       <c r="G146" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJDXgGzDfx</t>
@@ -5634,11 +5578,7 @@
           <t>FANFIC/K/02_伏八｜當鳳凰花開.md</t>
         </is>
       </c>
-      <c r="F147" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F147" s="6" t="n"/>
       <c r="G147" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HkdQlzfDMg</t>
@@ -5671,11 +5611,7 @@
           <t>FANFIC/K/03_伏八｜葬夢.md</t>
         </is>
       </c>
-      <c r="F148" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F148" s="6" t="n"/>
       <c r="G148" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkKmxGGvzx</t>
@@ -5708,11 +5644,7 @@
           <t>FANFIC/Sound Horizon/01_オリエレ｜極短.md</t>
         </is>
       </c>
-      <c r="F149" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F149" s="6" t="n"/>
       <c r="G149" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HysXlGzPMe</t>
@@ -5745,11 +5677,7 @@
           <t>FANFIC/Sound Horizon/02_オリエレ｜光.md</t>
         </is>
       </c>
-      <c r="F150" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F150" s="6" t="n"/>
       <c r="G150" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Hk2QlfMwfx</t>
@@ -5782,11 +5710,7 @@
           <t>FANFIC/Sound Horizon/03_オリエレ｜穿越陽光.md</t>
         </is>
       </c>
-      <c r="F151" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F151" s="6" t="n"/>
       <c r="G151" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJpmlfGwze</t>
@@ -5819,11 +5743,7 @@
           <t>FANFIC/Sound Horizon/04_オリエレ｜夢.md</t>
         </is>
       </c>
-      <c r="F152" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F152" s="6" t="n"/>
       <c r="G152" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkyVgfMvGe</t>
@@ -5856,11 +5776,7 @@
           <t>FANFIC/Sound Horizon/05_オリエレ｜學園極短.md</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F153" s="6" t="n"/>
       <c r="G153" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkeVezGPfl</t>
@@ -5893,11 +5809,7 @@
           <t>FANFIC/Sound Horizon/06_オリエレ｜債務未清.md</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F154" s="6" t="n"/>
       <c r="G154" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryG4lzfDMl</t>
@@ -5930,11 +5842,7 @@
           <t>FANFIC/Sound Horizon/07_オリエレ｜迷途.md</t>
         </is>
       </c>
-      <c r="F155" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F155" s="6" t="n"/>
       <c r="G155" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Sk7NlzfDzl</t>
@@ -5967,11 +5875,7 @@
           <t>FANFIC/Sound Horizon/08_オリエレ｜自欺.md</t>
         </is>
       </c>
-      <c r="F156" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F156" s="6" t="n"/>
       <c r="G156" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1ENxGfwfg</t>
@@ -6004,11 +5908,7 @@
           <t>FANFIC/Sound Horizon/09_オリエレ｜幻境.md</t>
         </is>
       </c>
-      <c r="F157" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F157" s="6" t="n"/>
       <c r="G157" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJIExzzvGe</t>
@@ -6041,11 +5941,7 @@
           <t>FANFIC/Sound Horizon/10_オリエレ｜思念傾覆之刻.md</t>
         </is>
       </c>
-      <c r="F158" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F158" s="6" t="n"/>
       <c r="G158" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SkwElzfDfg</t>
@@ -6078,11 +5974,7 @@
           <t>FANFIC/Sound Horizon/11_オリエレ｜事後補償.md</t>
         </is>
       </c>
-      <c r="F159" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F159" s="6" t="n"/>
       <c r="G159" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BkONeMzvfx</t>
@@ -6115,11 +6007,7 @@
           <t>FANFIC/Sound Horizon/12_オリエレ｜Constellation.md</t>
         </is>
       </c>
-      <c r="F160" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F160" s="6" t="n"/>
       <c r="G160" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SkqNxMzwGx</t>
@@ -6152,11 +6040,7 @@
           <t>FANFIC/Sound Horizon/13_オリエレ｜歸.md</t>
         </is>
       </c>
-      <c r="F161" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F161" s="6" t="n"/>
       <c r="G161" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1s4lMMDzg</t>
@@ -6189,11 +6073,7 @@
           <t>FANFIC/Sound Horizon/14_オリエレ｜起跑點.md</t>
         </is>
       </c>
-      <c r="F162" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F162" s="6" t="n"/>
       <c r="G162" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryhNezfDzg</t>
@@ -6226,11 +6106,7 @@
           <t>FANFIC/Sound Horizon/16_オリエレ｜晚間.md</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F163" s="6" t="n"/>
       <c r="G163" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SkkSgMfDGg</t>
@@ -6263,11 +6139,7 @@
           <t>FANFIC/Sound Horizon/17_オリエレ｜夜間.md</t>
         </is>
       </c>
-      <c r="F164" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F164" s="6" t="n"/>
       <c r="G164" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryeHlMfPGl</t>
@@ -6300,11 +6172,7 @@
           <t>FANFIC/Sound Horizon/18_オリエレ｜.md</t>
         </is>
       </c>
-      <c r="F165" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F165" s="6" t="n"/>
       <c r="G165" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1bBeMfPMx</t>
@@ -6337,11 +6205,7 @@
           <t>FANFIC/Sound Horizon/19_オリエレ｜晨間.md</t>
         </is>
       </c>
-      <c r="F166" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F166" s="6" t="n"/>
       <c r="G166" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJQrgfMwMl</t>
@@ -6374,11 +6238,7 @@
           <t>FANFIC/Sound Horizon/21_オリエレ｜同居30題.md</t>
         </is>
       </c>
-      <c r="F167" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F167" s="6" t="n"/>
       <c r="G167" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1SrgGGPGl</t>
@@ -6411,11 +6271,7 @@
           <t>FANFIC/Sound Horizon/15_Scorpius+Orion→Elef｜前刻.md</t>
         </is>
       </c>
-      <c r="F168" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F168" s="6" t="n"/>
       <c r="G168" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Bk6VlfGvMx</t>
@@ -6448,11 +6304,7 @@
           <t>FANFIC/Sound Horizon/20_Orion+Scorpius｜秋季來臨時.md</t>
         </is>
       </c>
-      <c r="F169" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F169" s="6" t="n"/>
       <c r="G169" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ByErxMzwMx</t>
@@ -6485,11 +6337,7 @@
           <t>FANFIC/Sound Horizon/22_オリスコ｜體溫至上主義.md</t>
         </is>
       </c>
-      <c r="F170" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F170" s="6" t="n"/>
       <c r="G170" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HkDSezzDfg</t>
@@ -6522,11 +6370,7 @@
           <t>FANFIC/Sound Horizon/23_Scorpius中心｜Weight of the World.md</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F171" s="6" t="n"/>
       <c r="G171" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SkOSeMfDMg</t>
@@ -6559,11 +6403,7 @@
           <t>FANFIC/あんスタ/01_傘.md</t>
         </is>
       </c>
-      <c r="F172" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F172" s="6" t="n"/>
       <c r="G172" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJFBeffvzx</t>
@@ -6596,11 +6436,7 @@
           <t>FANFIC/あんスタ/02_於心不忍.md</t>
         </is>
       </c>
-      <c r="F173" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F173" s="6" t="n"/>
       <c r="G173" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJsrxGzvzx</t>
@@ -6633,11 +6469,7 @@
           <t>FANFIC/あんスタ/03_幼時迴廊.md</t>
         </is>
       </c>
-      <c r="F174" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F174" s="6" t="n"/>
       <c r="G174" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1nSxMGDfx</t>
@@ -6670,11 +6502,7 @@
           <t>FANFIC/あんスタ/04_預謀犯罪.md</t>
         </is>
       </c>
-      <c r="F175" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F175" s="6" t="n"/>
       <c r="G175" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Bk6HlGfvMl</t>
@@ -6707,11 +6535,7 @@
           <t>FANFIC/あんスタ/05_Blue Daze.md</t>
         </is>
       </c>
-      <c r="F176" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F176" s="6" t="n"/>
       <c r="G176" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJ0rgzfvGl</t>
@@ -6744,11 +6568,7 @@
           <t>FANFIC/あんスタ/06_偶訪.md</t>
         </is>
       </c>
-      <c r="F177" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F177" s="6" t="n"/>
       <c r="G177" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/B1yIxzGwzg</t>
@@ -6781,11 +6601,7 @@
           <t>FANFIC/あんスタ/07_知道或不知道的.md</t>
         </is>
       </c>
-      <c r="F178" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F178" s="6" t="n"/>
       <c r="G178" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkeIgfzDMe</t>
@@ -6818,11 +6634,7 @@
           <t>FANFIC/あんスタ/08_許久未見.md</t>
         </is>
       </c>
-      <c r="F179" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F179" s="6" t="n"/>
       <c r="G179" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJMLlMMPGl</t>
@@ -6855,11 +6667,7 @@
           <t>FANFIC/あんスタ/09_巡夢.md</t>
         </is>
       </c>
-      <c r="F180" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F180" s="6" t="n"/>
       <c r="G180" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJQIgfzwzx</t>
@@ -6892,11 +6700,7 @@
           <t>FANFIC/あんスタ/10_慾望把眼前的地板鋪滿(凜零).md</t>
         </is>
       </c>
-      <c r="F181" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F181" s="6" t="n"/>
       <c r="G181" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1E8gzzPGx</t>
@@ -6929,11 +6733,7 @@
           <t>FANFIC/あんスタ/11_夏日營隊.md</t>
         </is>
       </c>
-      <c r="F182" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F182" s="6" t="n"/>
       <c r="G182" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkS8eGGPzg</t>
@@ -6966,11 +6766,7 @@
           <t>FANFIC/あんスタ/12_擁抱的力度.md</t>
         </is>
       </c>
-      <c r="F183" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F183" s="6" t="n"/>
       <c r="G183" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1UIeMGDzg</t>
@@ -7003,11 +6799,7 @@
           <t>FANFIC/あんスタ/13_花吐病.md</t>
         </is>
       </c>
-      <c r="F184" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F184" s="6" t="n"/>
       <c r="G184" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJDLlfMDGl</t>
@@ -7040,11 +6832,7 @@
           <t>FANFIC/あんスタ/14_是開始也是結束之地.md</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F185" s="6" t="n"/>
       <c r="G185" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/B1d8xfMDGe</t>
@@ -7077,11 +6865,7 @@
           <t>FANFIC/あんスタ/15_亞伯與該隱.md</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F186" s="6" t="n"/>
       <c r="G186" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJYLezfPMg</t>
@@ -7114,11 +6898,7 @@
           <t>FANFIC/あんスタ/16_眼神.md</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F187" s="6" t="n"/>
       <c r="G187" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1sUgzfDfl</t>
@@ -7151,11 +6931,7 @@
           <t>FANFIC/あんスタ/17_蒙布朗.md</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F188" s="6" t="n"/>
       <c r="G188" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Sy2IlfMwze</t>
@@ -7188,11 +6964,7 @@
           <t>FANFIC/あんスタ/18_想念.md</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F189" s="6" t="n"/>
       <c r="G189" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rypLgMGPMl</t>
@@ -7225,11 +6997,7 @@
           <t>FANFIC/あんスタ/19_尚且相慕的日子裡.md</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F190" s="6" t="n"/>
       <c r="G190" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryRIlzfDze</t>
@@ -7262,11 +7030,7 @@
           <t>FANFIC/あんスタ/20_手.md</t>
         </is>
       </c>
-      <c r="F191" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F191" s="6" t="n"/>
       <c r="G191" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r11DeGfvMx</t>
@@ -7299,11 +7063,7 @@
           <t>FANFIC/あんスタ/21_早安(薰奏薰).md</t>
         </is>
       </c>
-      <c r="F192" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F192" s="6" t="n"/>
       <c r="G192" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryZweGMDGe</t>
@@ -7336,11 +7096,7 @@
           <t>FANFIC/あんスタ/22_後青春幻想.md</t>
         </is>
       </c>
-      <c r="F193" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F193" s="6" t="n"/>
       <c r="G193" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJoP-MGPzg</t>
@@ -7373,11 +7129,7 @@
           <t>FANFIC/あんスタ/23_約.md</t>
         </is>
       </c>
-      <c r="F194" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F194" s="6" t="n"/>
       <c r="G194" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Byk_bMzDMe</t>
@@ -7439,11 +7191,7 @@
           <t>FANFIC/あんスタ/25_低潮.md</t>
         </is>
       </c>
-      <c r="F196" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F196" s="6" t="n"/>
       <c r="G196" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SkIubMzDfx</t>
@@ -7476,11 +7224,7 @@
           <t>FANFIC/あんスタ/26_突如其來的親吻.md</t>
         </is>
       </c>
-      <c r="F197" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F197" s="6" t="n"/>
       <c r="G197" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1qdbGGwzg</t>
@@ -7513,11 +7257,7 @@
           <t>FANFIC/あんスタ/27_未曾訴說的.md</t>
         </is>
       </c>
-      <c r="F198" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F198" s="6" t="n"/>
       <c r="G198" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJadZfMPMx</t>
@@ -7550,11 +7290,7 @@
           <t>FANFIC/あんスタ/28_弄傻.md</t>
         </is>
       </c>
-      <c r="F199" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F199" s="6" t="n"/>
       <c r="G199" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rk-Y-GGvfl</t>
@@ -7587,11 +7323,7 @@
           <t>FANFIC/あんスタ/29_賭.md</t>
         </is>
       </c>
-      <c r="F200" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F200" s="6" t="n"/>
       <c r="G200" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Bk4tbGMvzx</t>
@@ -7624,11 +7356,7 @@
           <t>FANFIC/あんスタ/30_未來所向.md</t>
         </is>
       </c>
-      <c r="F201" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F201" s="6" t="n"/>
       <c r="G201" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJuKZfzDMl</t>
@@ -7661,11 +7389,7 @@
           <t>FANFIC/あんスタ/31_偶有難解低潮拍打上岸.md</t>
         </is>
       </c>
-      <c r="F202" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F202" s="6" t="n"/>
       <c r="G202" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/B13tWMMDzx</t>
@@ -7698,11 +7422,7 @@
           <t>FANFIC/あんスタ/32_親吻.md</t>
         </is>
       </c>
-      <c r="F203" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F203" s="6" t="n"/>
       <c r="G203" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rky9ZMzvGe</t>
@@ -7735,11 +7455,7 @@
           <t>FANFIC/あんスタ/33_眼前只見.md</t>
         </is>
       </c>
-      <c r="F204" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F204" s="6" t="n"/>
       <c r="G204" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJm9ZfMvfl</t>
@@ -7772,11 +7488,7 @@
           <t>FANFIC/あんスタ/34_說了再見.md</t>
         </is>
       </c>
-      <c r="F205" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F205" s="6" t="n"/>
       <c r="G205" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Hy85ZGzDGg</t>
@@ -7809,11 +7521,7 @@
           <t>FANFIC/あんスタ/35_再相逢(獅心).md</t>
         </is>
       </c>
-      <c r="F206" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F206" s="6" t="n"/>
       <c r="G206" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJq5WfMDfx</t>
@@ -7846,11 +7554,7 @@
           <t>FANFIC/あんスタ/36_柔軟一如水母的毒刺.md</t>
         </is>
       </c>
-      <c r="F207" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F207" s="6" t="n"/>
       <c r="G207" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SkacWMGDzl</t>
@@ -7883,11 +7587,7 @@
           <t>FANFIC/あんスタ/37_癖好.md</t>
         </is>
       </c>
-      <c r="F208" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F208" s="6" t="n"/>
       <c r="G208" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryWjWzfvzl</t>
@@ -7920,11 +7620,7 @@
           <t>FANFIC/あんスタ/38_心中尚未崩壞的地方.md</t>
         </is>
       </c>
-      <c r="F209" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F209" s="6" t="n"/>
       <c r="G209" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1So-zMDGl</t>
@@ -7957,11 +7653,7 @@
           <t>FANFIC/あんスタ/39_熱戀中.md</t>
         </is>
       </c>
-      <c r="F210" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F210" s="6" t="n"/>
       <c r="G210" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BkKjbMGDfl</t>
@@ -7994,11 +7686,7 @@
           <t>FANFIC/あんスタ/40_無以名狀.md</t>
         </is>
       </c>
-      <c r="F211" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F211" s="6" t="n"/>
       <c r="G211" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1hjZGGDzx</t>
@@ -8031,11 +7719,7 @@
           <t>FANFIC/あんスタ/41_約會.md</t>
         </is>
       </c>
-      <c r="F212" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F212" s="6" t="n"/>
       <c r="G212" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1gnbGGDMg</t>
@@ -8068,11 +7752,7 @@
           <t>FANFIC/あんスタ/42_花白如雪.md</t>
         </is>
       </c>
-      <c r="F213" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F213" s="6" t="n"/>
       <c r="G213" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1X3-MzwMe</t>
@@ -8105,11 +7785,7 @@
           <t>FANFIC/あんスタ/43_夢(北涉).md</t>
         </is>
       </c>
-      <c r="F214" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F214" s="6" t="n"/>
       <c r="G214" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Hkv2WzfDfx</t>
@@ -8142,11 +7818,7 @@
           <t>FANFIC/あんスタ/44_終有一日(凜緒).md</t>
         </is>
       </c>
-      <c r="F215" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F215" s="6" t="n"/>
       <c r="G215" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1ohWGMvMl</t>
@@ -8179,11 +7851,7 @@
           <t>FANFIC/あんスタ/45_晚安(阿多薰).md</t>
         </is>
       </c>
-      <c r="F216" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F216" s="6" t="n"/>
       <c r="G216" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJRnWMfwMe</t>
@@ -8216,11 +7884,7 @@
           <t>FANFIC/あんスタ/46_隨筆(千薰♀).md</t>
         </is>
       </c>
-      <c r="F217" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F217" s="6" t="n"/>
       <c r="G217" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkMp-zMPfe</t>
@@ -8253,11 +7917,7 @@
           <t>FANFIC/あんスタ/47_牽手(涉奏涉).md</t>
         </is>
       </c>
-      <c r="F218" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F218" s="6" t="n"/>
       <c r="G218" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/B1rpZfMDfl</t>
@@ -8290,11 +7950,7 @@
           <t>FANFIC/あんスタ/48_人之初(なずみかなず).md</t>
         </is>
       </c>
-      <c r="F219" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F219" s="6" t="n"/>
       <c r="G219" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJtT-zMDMg</t>
@@ -8327,11 +7983,7 @@
           <t>FANFIC/あんスタ/49_隨筆(深海中心).md</t>
         </is>
       </c>
-      <c r="F220" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F220" s="6" t="n"/>
       <c r="G220" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1naZMMvMg</t>
@@ -8364,11 +8016,7 @@
           <t>FANFIC/あんスタ/50_可曾知曉(薰あん).md</t>
         </is>
       </c>
-      <c r="F221" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F221" s="6" t="n"/>
       <c r="G221" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJgRZMfDfe</t>
@@ -8401,11 +8049,7 @@
           <t>FANFIC/三國/01_策瑜｜無賴.md</t>
         </is>
       </c>
-      <c r="F222" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F222" s="6" t="n"/>
       <c r="G222" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/B1ZMWfGvGl</t>
@@ -8438,11 +8082,7 @@
           <t>FANFIC/三國/02_策瑜｜葉笛.md</t>
         </is>
       </c>
-      <c r="F223" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F223" s="6" t="n"/>
       <c r="G223" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkfzWGGDfe</t>
@@ -8475,11 +8115,7 @@
           <t>FANFIC/三國/03_策瑜｜月酒.md</t>
         </is>
       </c>
-      <c r="F224" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F224" s="6" t="n"/>
       <c r="G224" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Hk7fbfzDfl</t>
@@ -8512,11 +8148,7 @@
           <t>FANFIC/家教/01_骸綱｜許久.md</t>
         </is>
       </c>
-      <c r="F225" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F225" s="6" t="n"/>
       <c r="G225" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rySGbfzPMl</t>
@@ -8549,11 +8181,7 @@
           <t>FANFIC/家教/02_骸綱｜崩落.md</t>
         </is>
       </c>
-      <c r="F226" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F226" s="6" t="n"/>
       <c r="G226" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkUz-fGDGe</t>
@@ -8586,11 +8214,7 @@
           <t>FANFIC/家教/03_骸綱｜業火.md</t>
         </is>
       </c>
-      <c r="F227" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F227" s="6" t="n"/>
       <c r="G227" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SkwzbGMPGe</t>
@@ -8623,11 +8247,7 @@
           <t>FANFIC/家教/04_骸綱｜Death.md</t>
         </is>
       </c>
-      <c r="F228" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F228" s="6" t="n"/>
       <c r="G228" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HkOGbzfDGl</t>
@@ -8660,11 +8280,7 @@
           <t>FANFIC/家教/06_骸綱｜無須同情.md</t>
         </is>
       </c>
-      <c r="F229" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F229" s="6" t="n"/>
       <c r="G229" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BkqfbfzDfe</t>
@@ -8697,11 +8313,7 @@
           <t>FANFIC/家教/07_骸綱｜遊.md</t>
         </is>
       </c>
-      <c r="F230" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F230" s="6" t="n"/>
       <c r="G230" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJhMZzGDfg</t>
@@ -8734,11 +8346,7 @@
           <t>FANFIC/家教/05_里藍｜強迫推銷.md</t>
         </is>
       </c>
-      <c r="F231" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F231" s="6" t="n"/>
       <c r="G231" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1FG-MzvGl</t>
@@ -8771,11 +8379,7 @@
           <t>FANFIC/弱虫ペダル/01_隨筆(真東)妖怪趴囉.md</t>
         </is>
       </c>
-      <c r="F232" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F232" s="6" t="n"/>
       <c r="G232" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rk6MbGMDMg</t>
@@ -8808,11 +8412,7 @@
           <t>FANFIC/弱虫ペダル/02_銀河鉄道の夜.md</t>
         </is>
       </c>
-      <c r="F233" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F233" s="6" t="n"/>
       <c r="G233" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1RzbzfDzx</t>
@@ -8845,11 +8445,7 @@
           <t>FANFIC/弱虫ペダル/03_偶訪(真東).md</t>
         </is>
       </c>
-      <c r="F234" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F234" s="6" t="n"/>
       <c r="G234" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ByyQWffwfx</t>
@@ -8882,11 +8478,7 @@
           <t>FANFIC/弱虫ペダル/04_名為祝福的甜膩詛咒.md</t>
         </is>
       </c>
-      <c r="F235" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F235" s="6" t="n"/>
       <c r="G235" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryeXZGGvGe</t>
@@ -8919,11 +8511,7 @@
           <t>FANFIC/弱虫ペダル/05_粉絲.md</t>
         </is>
       </c>
-      <c r="F236" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F236" s="6" t="n"/>
       <c r="G236" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryZXWfGwfe</t>
@@ -8956,11 +8544,7 @@
           <t>FANFIC/弱虫ペダル/06_戀愛這檔事01.md</t>
         </is>
       </c>
-      <c r="F237" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F237" s="6" t="n"/>
       <c r="G237" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJ7X-fMPfe</t>
@@ -8993,11 +8577,7 @@
           <t>FANFIC/弱虫ペダル/07_戀愛這檔事02.md</t>
         </is>
       </c>
-      <c r="F238" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F238" s="6" t="n"/>
       <c r="G238" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1VXZfGDze</t>
@@ -9030,11 +8610,7 @@
           <t>FANFIC/弱虫ペダル/08_墜入情網的瞬間.md</t>
         </is>
       </c>
-      <c r="F239" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F239" s="6" t="n"/>
       <c r="G239" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJBmZfGwMl</t>
@@ -9067,11 +8643,7 @@
           <t>FANFIC/弱虫ペダル/09_毫無反應只是肉 01.md</t>
         </is>
       </c>
-      <c r="F240" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F240" s="6" t="n"/>
       <c r="G240" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SkUQ-fMDzg</t>
@@ -9104,11 +8676,7 @@
           <t>FANFIC/弱虫ペダル/10_毫無反應只是肉 02.md</t>
         </is>
       </c>
-      <c r="F241" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F241" s="6" t="n"/>
       <c r="G241" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Bk_mZMzDzx</t>
@@ -9141,11 +8709,7 @@
           <t>FANFIC/弱虫ペダル/11_TODO.avi.md</t>
         </is>
       </c>
-      <c r="F242" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F242" s="6" t="n"/>
       <c r="G242" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SyKmZMMPzl</t>
@@ -9178,11 +8742,7 @@
           <t>FANFIC/弱虫ペダル/12_歸時無路.md</t>
         </is>
       </c>
-      <c r="F243" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F243" s="6" t="n"/>
       <c r="G243" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1c7-zMwzx</t>
@@ -9215,11 +8775,7 @@
           <t>FANFIC/弱虫ペダル/13_順理成章的白日宣淫.md</t>
         </is>
       </c>
-      <c r="F244" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F244" s="6" t="n"/>
       <c r="G244" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r12Q-zfDzl</t>
@@ -9252,11 +8808,7 @@
           <t>FANFIC/弱虫ペダル/14_Bad bad dream.md</t>
         </is>
       </c>
-      <c r="F245" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F245" s="6" t="n"/>
       <c r="G245" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1am-fzDfx</t>
@@ -9289,11 +8841,7 @@
           <t>FANFIC/弱虫ペダル/15_初夜.md</t>
         </is>
       </c>
-      <c r="F246" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F246" s="6" t="n"/>
       <c r="G246" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryCXbzGPGl</t>
@@ -9326,11 +8874,7 @@
           <t>FANFIC/弱虫ペダル/16_Tacit.md</t>
         </is>
       </c>
-      <c r="F247" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F247" s="6" t="n"/>
       <c r="G247" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1y4bzfwGe</t>
@@ -9363,11 +8907,7 @@
           <t>FANFIC/弱虫ペダル/17_酷熱的日子裡最難以忍受的病因 (真東).md</t>
         </is>
       </c>
-      <c r="F248" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F248" s="6" t="n"/>
       <c r="G248" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1ZNZGfwMe</t>
@@ -9400,11 +8940,7 @@
           <t>FANFIC/弱虫ペダル/18_窗 (宮→真東).md</t>
         </is>
       </c>
-      <c r="F249" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F249" s="6" t="n"/>
       <c r="G249" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1GVZGzPfe</t>
@@ -9437,11 +8973,7 @@
           <t>FANFIC/弱虫ペダル/19_那些屬於我們的日子.md</t>
         </is>
       </c>
-      <c r="F250" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F250" s="6" t="n"/>
       <c r="G250" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJ7VbMGwzg</t>
@@ -9474,11 +9006,7 @@
           <t>FANFIC/弱虫ペダル/20_暖冬.md</t>
         </is>
       </c>
-      <c r="F251" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F251" s="6" t="n"/>
       <c r="G251" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJVNWMzwGl</t>
@@ -9511,11 +9039,7 @@
           <t>FANFIC/弱虫ペダル/21_三月春雨.md</t>
         </is>
       </c>
-      <c r="F252" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F252" s="6" t="n"/>
       <c r="G252" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJUEZGGwzx</t>
@@ -9548,11 +9072,7 @@
           <t>FANFIC/弱虫ペダル/22_隨筆(真東).md</t>
         </is>
       </c>
-      <c r="F253" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F253" s="6" t="n"/>
       <c r="G253" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BkDEWffPfe</t>
@@ -9585,11 +9105,7 @@
           <t>FANFIC/弱虫ペダル/23_酷熱的日子裡最難以忍受的病因 (荒東)-2.md</t>
         </is>
       </c>
-      <c r="F254" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F254" s="6" t="n"/>
       <c r="G254" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJ_V-GMDzl</t>
@@ -9622,11 +9138,7 @@
           <t>FANFIC/弱虫ペダル/24_隨筆(荒東).md</t>
         </is>
       </c>
-      <c r="F255" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F255" s="6" t="n"/>
       <c r="G255" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJFEWMGwGg</t>
@@ -9659,11 +9171,7 @@
           <t>FANFIC/弱虫ペダル/25_未知此刻.md</t>
         </is>
       </c>
-      <c r="F256" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F256" s="6" t="n"/>
       <c r="G256" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Sk9V-fMvMe</t>
@@ -9696,11 +9204,7 @@
           <t>FANFIC/弱虫ペダル/26_酷熱的日子裡最難以忍受的病因(荒東).md</t>
         </is>
       </c>
-      <c r="F257" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F257" s="6" t="n"/>
       <c r="G257" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryn4-MfPze</t>
@@ -9733,11 +9237,7 @@
           <t>FANFIC/弱虫ペダル/27_慾望把眼前的地板鋪滿(荒東).md</t>
         </is>
       </c>
-      <c r="F258" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F258" s="6" t="n"/>
       <c r="G258" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ByTV-GzDMe</t>
@@ -9770,11 +9270,7 @@
           <t>FANFIC/弱虫ペダル/28_祭.md</t>
         </is>
       </c>
-      <c r="F259" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F259" s="6" t="n"/>
       <c r="G259" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BkC4-fMPzg</t>
@@ -9807,11 +9303,7 @@
           <t>FANFIC/弱虫ペダル/29_深秋.md</t>
         </is>
       </c>
-      <c r="F260" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F260" s="6" t="n"/>
       <c r="G260" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkkrbfGvMg</t>
@@ -9844,11 +9336,7 @@
           <t>FANFIC/弱虫ペダル/30_星期六、耳朵軟骨、降雨機率88%.md</t>
         </is>
       </c>
-      <c r="F261" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F261" s="6" t="n"/>
       <c r="G261" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1xH-fGPGe</t>
@@ -9881,11 +9369,7 @@
           <t>FANFIC/弱虫ペダル/31_酷熱的日子裡最難以忍受的病因(東真).md</t>
         </is>
       </c>
-      <c r="F262" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F262" s="6" t="n"/>
       <c r="G262" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SybSWzMwMx</t>
@@ -9918,11 +9402,7 @@
           <t>FANFIC/弱虫ペダル/32_隨筆(東真).md</t>
         </is>
       </c>
-      <c r="F263" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F263" s="6" t="n"/>
       <c r="G263" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1QHbfMPMl</t>
@@ -9955,11 +9435,7 @@
           <t>FANFIC/弱虫ペダル/33_鴛鴦浴.md</t>
         </is>
       </c>
-      <c r="F264" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F264" s="6" t="n"/>
       <c r="G264" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJVr-zzDGl</t>
@@ -9992,11 +9468,7 @@
           <t>FANFIC/弱虫ペダル/34_柔軟度.md</t>
         </is>
       </c>
-      <c r="F265" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F265" s="6" t="n"/>
       <c r="G265" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJBH-GzPMx</t>
@@ -10029,11 +9501,7 @@
           <t>FANFIC/弱虫ペダル/35_練筆(東卷).md</t>
         </is>
       </c>
-      <c r="F266" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F266" s="6" t="n"/>
       <c r="G266" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H18rWMfwfx</t>
@@ -10066,11 +9534,7 @@
           <t>FANFIC/弱虫ペダル/36_天氣晴.md</t>
         </is>
       </c>
-      <c r="F267" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F267" s="6" t="n"/>
       <c r="G267" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkvHZzfPMg</t>
@@ -10103,11 +9567,7 @@
           <t>FANFIC/弱虫ペダル/37_髮.md</t>
         </is>
       </c>
-      <c r="F268" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F268" s="6" t="n"/>
       <c r="G268" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rk_BbMfvGe</t>
@@ -10140,11 +9600,7 @@
           <t>FANFIC/Free!/01_愛凜｜如何跟前輩打好關係.md</t>
         </is>
       </c>
-      <c r="F269" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F269" s="6" t="n"/>
       <c r="G269" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkB9kMfDMl</t>
@@ -10177,11 +9633,7 @@
           <t>FANFIC/Free!/02_愛凜｜盛夏之時01.md</t>
         </is>
       </c>
-      <c r="F270" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F270" s="6" t="n"/>
       <c r="G270" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Hkv5JMzvMx</t>
@@ -10214,11 +9666,7 @@
           <t>FANFIC/Free!/03_愛凜｜盛夏之時02.md</t>
         </is>
       </c>
-      <c r="F271" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F271" s="6" t="n"/>
       <c r="G271" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJu51GGvfg</t>
@@ -10251,11 +9699,7 @@
           <t>FANFIC/Free!/04_愛凜｜盛夏之時03.md</t>
         </is>
       </c>
-      <c r="F272" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F272" s="6" t="n"/>
       <c r="G272" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Sy9cyzfwzx</t>
@@ -10288,11 +9732,7 @@
           <t>FANFIC/Free!/05_愛凜｜盛夏之時04.md</t>
         </is>
       </c>
-      <c r="F273" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F273" s="6" t="n"/>
       <c r="G273" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/B1ickMGDMx</t>
@@ -10325,11 +9765,7 @@
           <t>FANFIC/Free!/06_愛凜｜盛夏之時05.md</t>
         </is>
       </c>
-      <c r="F274" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F274" s="6" t="n"/>
       <c r="G274" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1hqyzMPMe</t>
@@ -10362,11 +9798,7 @@
           <t>FANFIC/Free!/07_愛凜｜盛夏之時06.md</t>
         </is>
       </c>
-      <c r="F275" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F275" s="6" t="n"/>
       <c r="G275" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJ09kzGPGl</t>
@@ -10399,11 +9831,7 @@
           <t>FANFIC/Free!/08_愛凜｜盛夏之時07.md</t>
         </is>
       </c>
-      <c r="F276" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F276" s="6" t="n"/>
       <c r="G276" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HyJjyzMwzg</t>
@@ -10436,11 +9864,7 @@
           <t>FANFIC/Free!/09_愛凜｜盛夏之時08.md</t>
         </is>
       </c>
-      <c r="F277" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F277" s="6" t="n"/>
       <c r="G277" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HkWo1GGDMx</t>
@@ -10473,11 +9897,7 @@
           <t>FANFIC/Free!/10_愛凜｜盛夏之時09.md</t>
         </is>
       </c>
-      <c r="F278" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F278" s="6" t="n"/>
       <c r="G278" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/B1GoJMfwfl</t>
@@ -10510,11 +9930,7 @@
           <t>FANFIC/Free!/11_愛凜｜盛夏之時10.md</t>
         </is>
       </c>
-      <c r="F279" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F279" s="6" t="n"/>
       <c r="G279" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1ms1fMwfl</t>
@@ -10547,11 +9963,7 @@
           <t>FANFIC/Free!/12_愛凜｜盛夏之時11.md</t>
         </is>
       </c>
-      <c r="F280" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F280" s="6" t="n"/>
       <c r="G280" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryHs1GfvMl</t>
@@ -10584,11 +9996,7 @@
           <t>FANFIC/Free!/13_愛凜｜盛夏之時12.md</t>
         </is>
       </c>
-      <c r="F281" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F281" s="6" t="n"/>
       <c r="G281" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJLokzGPGl</t>
@@ -10621,11 +10029,7 @@
           <t>FANFIC/Free!/14_愛凜｜盛夏之時13.md</t>
         </is>
       </c>
-      <c r="F282" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F282" s="6" t="n"/>
       <c r="G282" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ry_j1GMPMl</t>
@@ -10658,11 +10062,7 @@
           <t>FANFIC/Free!/15_愛凜｜盛夏之時14.md</t>
         </is>
       </c>
-      <c r="F283" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F283" s="6" t="n"/>
       <c r="G283" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BkYikzfwzx</t>
@@ -10695,11 +10095,7 @@
           <t>FANFIC/Free!/16_愛凜｜盛夏之時15.md</t>
         </is>
       </c>
-      <c r="F284" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F284" s="6" t="n"/>
       <c r="G284" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H15skMfvfl</t>
@@ -10732,11 +10128,7 @@
           <t>FANFIC/Free!/17_愛凜｜盛夏之時16.md</t>
         </is>
       </c>
-      <c r="F285" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F285" s="6" t="n"/>
       <c r="G285" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryho1fMwGe</t>
@@ -10769,11 +10161,7 @@
           <t>FANFIC/Free!/18_愛凜｜盛夏之時17.md</t>
         </is>
       </c>
-      <c r="F286" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F286" s="6" t="n"/>
       <c r="G286" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/B16jkGfwMe</t>
@@ -10806,11 +10194,7 @@
           <t>FANFIC/Free!/19_愛凜｜盛夏之時18.md</t>
         </is>
       </c>
-      <c r="F287" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F287" s="6" t="n"/>
       <c r="G287" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJyhkMGvMx</t>
@@ -10843,11 +10227,7 @@
           <t>FANFIC/Free!/20_愛凜｜盛夏之時19-22.md</t>
         </is>
       </c>
-      <c r="F288" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F288" s="6" t="n"/>
       <c r="G288" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BklhkMGPzx</t>
@@ -10880,11 +10260,7 @@
           <t>FANFIC/Free!/21_愛凜｜盛夏之時23-25(完).md</t>
         </is>
       </c>
-      <c r="F289" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F289" s="6" t="n"/>
       <c r="G289" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJfhyzGPzl</t>
@@ -10917,11 +10293,7 @@
           <t>FANFIC/Free!/22_愛凜｜背入、深夜、似鳥的床上。.md</t>
         </is>
       </c>
-      <c r="F290" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F290" s="6" t="n"/>
       <c r="G290" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJ72JGfDze</t>
@@ -10954,11 +10326,7 @@
           <t>FANFIC/Free!/23_愛凜｜盛夏之時番外.md</t>
         </is>
       </c>
-      <c r="F291" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F291" s="6" t="n"/>
       <c r="G291" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1N3yfMDfx</t>
@@ -10991,11 +10359,7 @@
           <t>FANFIC/護玄/02_因聿因｜癮.md</t>
         </is>
       </c>
-      <c r="F292" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F292" s="6" t="n"/>
       <c r="G292" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ByGIbMGDfe</t>
@@ -11028,11 +10392,7 @@
           <t>FANFIC/護玄/07_因聿因｜未若彼時.md</t>
         </is>
       </c>
-      <c r="F293" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F293" s="6" t="n"/>
       <c r="G293" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Syw3GffPMe</t>
@@ -11065,11 +10425,7 @@
           <t>FANFIC/護玄/03_夏千｜癒.md</t>
         </is>
       </c>
-      <c r="F294" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F294" s="6" t="n"/>
       <c r="G294" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJXIZzfPMe</t>
@@ -11102,11 +10458,7 @@
           <t>FANFIC/護玄/06_夏千｜歸時.md</t>
         </is>
       </c>
-      <c r="F295" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F295" s="6" t="n"/>
       <c r="G295" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/By43zzzPzl</t>
@@ -11139,11 +10491,7 @@
           <t>FANFIC/護玄/04_極地兄弟｜來訪.md</t>
         </is>
       </c>
-      <c r="F296" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F296" s="6" t="n"/>
       <c r="G296" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HyELZzzPfe</t>
@@ -11176,11 +10524,7 @@
           <t>FANFIC/護玄/01_火帝依利｜之後的偷閒.md</t>
         </is>
       </c>
-      <c r="F297" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F297" s="6" t="n"/>
       <c r="G297" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJbLZGMDzg</t>
@@ -11213,11 +10557,7 @@
           <t>FANFIC/護玄/05_暮、曦中心｜想.md</t>
         </is>
       </c>
-      <c r="F298" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F298" s="6" t="n"/>
       <c r="G298" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1e2GGMwzx</t>
@@ -11250,11 +10590,7 @@
           <t>FANFIC/黑子的籃球/01_紫冰｜練筆.md</t>
         </is>
       </c>
-      <c r="F299" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F299" s="6" t="n"/>
       <c r="G299" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Sk3hMfMPzl</t>
@@ -11287,11 +10623,7 @@
           <t>FANFIC/黑子的籃球/02_紫冰｜假日.md</t>
         </is>
       </c>
-      <c r="F300" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F300" s="6" t="n"/>
       <c r="G300" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkJTfGzvMx</t>
@@ -11324,11 +10656,7 @@
           <t>FANFIC/黑子的籃球/03_青黃｜偶爾.md</t>
         </is>
       </c>
-      <c r="F301" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F301" s="6" t="n"/>
       <c r="G301" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HyQ6fzMwGg</t>
@@ -11361,11 +10689,7 @@
           <t>FANFIC/黑子的籃球/04_赤黑｜期待.md</t>
         </is>
       </c>
-      <c r="F302" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F302" s="6" t="n"/>
       <c r="G302" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HkL6MMfPfg</t>
@@ -11398,11 +10722,7 @@
           <t>FANFIC/未分類/01_Ace｜致艾斯.md</t>
         </is>
       </c>
-      <c r="F303" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F303" s="6" t="n"/>
       <c r="G303" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1tH-fMvzg</t>
@@ -11435,11 +10755,7 @@
           <t>FANFIC/未分類/02_Bleach｜414-416觀後感.md</t>
         </is>
       </c>
-      <c r="F304" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F304" s="6" t="n"/>
       <c r="G304" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJsBbzGwGx</t>
@@ -11472,11 +10788,7 @@
           <t>FANFIC/未分類/03_眾作品｜極短.md</t>
         </is>
       </c>
-      <c r="F305" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F305" s="6" t="n"/>
       <c r="G305" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/B13r-GzPMx</t>
@@ -11509,11 +10821,7 @@
           <t>FANFIC/未分類/04_火影｜致宇智波鼬.md</t>
         </is>
       </c>
-      <c r="F306" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F306" s="6" t="n"/>
       <c r="G306" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkpHZGMvMe</t>
@@ -11546,11 +10854,7 @@
           <t>FANFIC/未分類/05_多CP｜大風一直吹.md</t>
         </is>
       </c>
-      <c r="F307" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F307" s="6" t="n"/>
       <c r="G307" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJAr-Gfwfx</t>
@@ -11583,11 +10887,7 @@
           <t>FANFIC/未分類/06_寫手精分七題｜多CP.md</t>
         </is>
       </c>
-      <c r="F308" s="6" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F308" s="6" t="n"/>
       <c r="G308" s="3" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SykIWMMwzx</t>
@@ -12257,12 +11557,12 @@
           <t>ORIGINAL/云飛弦/00_云飛弦｜角色介紹.md</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="n"/>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/SygrBxftfl</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -12290,12 +11590,12 @@
           <t>ORIGINAL/云飛弦/企劃主線/01_Day 0.md</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/H1GHSxzKGx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -12323,12 +11623,12 @@
           <t>ORIGINAL/云飛弦/企劃主線/02_Day 1.md</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/ry4Srlztfx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -12356,12 +11656,12 @@
           <t>ORIGINAL/云飛弦/企劃主線/03_Day 2.md</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/rkLrBeMYfx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -12389,12 +11689,12 @@
           <t>ORIGINAL/云飛弦/企劃主線/04_Day 3.md</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/rkuBHxfYzl</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -12422,12 +11722,12 @@
           <t>ORIGINAL/云飛弦/企劃主線/05_Day 4.md</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/HyFSHlGKfg</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -12455,12 +11755,12 @@
           <t>ORIGINAL/云飛弦/企劃主線/06_Day 5.md</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/BJsSrgftGl</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -12488,12 +11788,12 @@
           <t>ORIGINAL/云飛弦/企劃主線/07_Day 6.md</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/HJaBrlfYfe</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -12521,12 +11821,12 @@
           <t>ORIGINAL/云飛弦/企劃主線/08_Day 7.md</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/ryy8BxfKMl</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -12554,12 +11854,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/01_云 0.2.4.md</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/H1x8SgGKfe</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -12587,12 +11887,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/02_云 0.1.3.md</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/ByMLBefFMe</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -12620,12 +11920,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/03_云 0.0.0.md</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/SJE8rlMKMg</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -12653,12 +11953,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/04_云 0.2.5.md</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/r1I8HxfYGl</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -12686,12 +11986,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/05_云 0.1.1.md</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/HJwLSxMYGx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -12719,12 +12019,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/06_云 0.2.3.md</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/BJY8reMKMe</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -12752,12 +12052,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/07_云 0.2.1.md</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/SkjLBeMKGg</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -12785,12 +12085,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/08_云 0.1.4.md</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/Byh8rxMFGl</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -12818,12 +12118,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/09_云 0.0.2.md</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/S1A8BxGYGx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -12851,12 +12151,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/10_云 0.2.6.md</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/HklvrlGYGg</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -12884,12 +12184,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/11_云 0.1.6.md</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/r1MwHgMFMx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -12917,12 +12217,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/12_云 0.1.2.md</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/r1mDrgfKMg</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -12950,12 +12250,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/13_云 0.0.1.md</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/ryBPSxGtzg</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -12983,12 +12283,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/14_云 0.1.5.md</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n"/>
+      <c r="F24" s="6" t="n"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/BkwPrgGtzg</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -13016,12 +12316,12 @@
           <t>ORIGINAL/云飛弦/企劃短打/15_云 0.2.7.md</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="n"/>
+      <c r="F25" s="6" t="n"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/SJFDrlfKGg</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -13049,12 +12349,12 @@
           <t>ORIGINAL/云飛弦/Others/01_春臨(咪金).md</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/SkqPBxMKGl</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -13082,12 +12382,12 @@
           <t>ORIGINAL/云飛弦/Others/02_暮曙光(歐爾Q).md</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/ryhPHxftGe</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -13115,12 +12415,12 @@
           <t>ORIGINAL/云飛弦/Others/03_重逢、涅斯托耳之杯、殘缺的聖歌(云飛弦).md</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/H1CPBeGtMg</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -13148,12 +12448,12 @@
           <t>ORIGINAL/云飛弦/Others/04_提爐香船、漆黑的砂土、圓舞曲(歐爾頓).md</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/HyxdHxzFfx</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -13181,12 +12481,12 @@
           <t>ORIGINAL/云飛弦/Others/05_永生花、忒修斯之船、晨曦(？？？).md</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/HJM_HgzKGg</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -13214,12 +12514,12 @@
           <t>ORIGINAL/云飛弦/Others/06_雙人舞、瓦爾普吉斯之夜、水晶杯(咪金).md</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/SJmuSlGKzx</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -13247,12 +12547,12 @@
           <t>ORIGINAL/云飛弦/非企內文章/01_筑云前導.md</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n"/>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/H1rOBeztzg</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -15097,11 +14397,7 @@
           <t>ORIGINAL/非企劃原創/02_帝燣｜新居日常.md</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F89" s="7" t="n"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkE9mMGPMe</t>
@@ -15134,11 +14430,7 @@
           <t>ORIGINAL/非企劃原創/01_帝燣｜Date.md</t>
         </is>
       </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>更新</t>
-        </is>
-      </c>
+      <c r="F90" s="7" t="n"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJFKXffwMl</t>

--- a/_sync/HackMD同步對照表.xlsx
+++ b/_sync/HackMD同步對照表.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>GitHub repo 內的相對路徑，供「更新」動作使用</t>
+          <t>GitHub repo 內的相對路徑。新增與更新都會讀這個路徑，不可留空</t>
         </is>
       </c>
     </row>
@@ -614,98 +614,98 @@
     <row r="15" ht="27.6" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>新增文章：把檔案放進 GitHub 並 push，在表格加一行，動作欄填「新增」，網址留空</t>
+          <t>第一次使用：雙擊 _sync\首次設定.bat，貼上 HackMD API Token。只需做一次，之後會永久記住</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>修改文章：改好檔案並 push，找到該行，動作欄填「更新」</t>
+          <t>新增文章：把 md 檔放進 repo 資料夾，在表格加一行，動作欄填「新增」，網址留空</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>刪除文章：找到該行，動作欄填「刪除」（程式會先列出清單請你確認）</t>
+          <t>修改文章：改好 md 檔，找到該行，動作欄填「更新」</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>調整順序：直接上下搬動整列即可，同分區的列請保持連續</t>
+          <t>刪除文章：找到該行，動作欄填「刪除」（程式會先列出清單請你確認）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>調整順序：直接上下搬動整列即可，同分區的列請保持連續</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>存檔後執行同步程式，程式會重新產生四本目錄並清空已處理的動作欄</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="2" t="n"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>存檔並關掉 Excel，然後雙擊 _sync\同步.bat</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>只調整過順序、沒有要新增或修改時，改雙擊 _sync\只重建目錄.bat</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>注意事項</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>刪除動作不可逆，執行前程式會要求輸入 yes 確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>章節與分區的出現順序，決定目錄上的排列順序</t>
-        </is>
-      </c>
+      <c r="B23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -715,7 +715,67 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>刪除動作不可逆，執行前程式會要求輸入 yes 確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>章節與分區的出現順序，決定目錄上的排列順序</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>黃底的「動作」欄是唯一需要你經常填寫的欄位</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>跑完後打開表格確認動作欄已全空。還有值代表那幾列失敗了，修好後再跑一次即可</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>不需要先 push 到 GitHub 也能同步，程式讀的是本機檔案。push 只是讓 GitHub 上的版本跟著更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>HackMD API 額度：Prime 每月 20,000 次、每 5 分鐘 100 次。一篇文章算一次，撞到速率限制時程式會自動等待重試</t>
         </is>
       </c>
     </row>

--- a/_sync/HackMD同步對照表.xlsx
+++ b/_sync/HackMD同步對照表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FANFIC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ORIGINAL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commission" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="雜文" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="說明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FANFIC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ORIGINAL" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Commission" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="雜文" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -537,7 +537,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="78" customWidth="1" min="2" max="2"/>
@@ -1051,7 +1051,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I500"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="9.875" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -15289,7 +15289,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I501"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="30" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="30" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="9" min="1" max="1"/>
     <col width="16.25" bestFit="1" customWidth="1" style="9" min="2" max="2"/>
@@ -21272,7 +21272,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I500"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -25017,7 +25017,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I499"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>

--- a/_sync/HackMD同步對照表.xlsx
+++ b/_sync/HackMD同步對照表.xlsx
@@ -15288,7 +15288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I501"/>
+  <dimension ref="A1:I502"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="30" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="9" min="1" max="1"/>
@@ -15416,7 +15416,11 @@
           <t>ORIGINAL/云飛弦/企劃主線/01_Day 0.md</t>
         </is>
       </c>
-      <c r="F3" s="6" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1GHSxzKGx</t>
@@ -15459,7 +15463,11 @@
           <t>ORIGINAL/云飛弦/企劃主線/02_Day 1.md</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ry4Srlztfx</t>
@@ -15502,7 +15510,11 @@
           <t>ORIGINAL/云飛弦/企劃主線/03_Day 2.md</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkLrBeMYfx</t>
@@ -15545,7 +15557,11 @@
           <t>ORIGINAL/云飛弦/企劃主線/04_Day 3.md</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkuBHxfYzl</t>
@@ -15588,7 +15604,11 @@
           <t>ORIGINAL/云飛弦/企劃主線/05_Day 4.md</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HyFSHlGKfg</t>
@@ -15631,7 +15651,11 @@
           <t>ORIGINAL/云飛弦/企劃主線/06_Day 5.md</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJsSrgftGl</t>
@@ -15674,7 +15698,11 @@
           <t>ORIGINAL/云飛弦/企劃主線/07_Day 6.md</t>
         </is>
       </c>
-      <c r="F9" s="6" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJaBrlfYfe</t>
@@ -15717,7 +15745,11 @@
           <t>ORIGINAL/云飛弦/企劃主線/08_Day 7.md</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryy8BxfKMl</t>
@@ -15760,7 +15792,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/03_云 0.0.0.md</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJE8rlMKMg</t>
@@ -15803,7 +15839,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/05_云 0.1.1.md</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJwLSxMYGx</t>
@@ -15846,7 +15886,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/01_云 0.2.4.md</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1x8SgGKfe</t>
@@ -15889,7 +15933,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/02_云 0.1.3.md</t>
         </is>
       </c>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ByMLBefFMe</t>
@@ -15932,7 +15980,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/04_云 0.2.5.md</t>
         </is>
       </c>
-      <c r="F15" s="6" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1I8HxfYGl</t>
@@ -15975,7 +16027,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/09_云 0.0.2.md</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/S1A8BxGYGx</t>
@@ -16018,7 +16074,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/06_云 0.2.3.md</t>
         </is>
       </c>
-      <c r="F17" s="6" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJY8reMKMe</t>
@@ -16061,7 +16121,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/07_云 0.2.1.md</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SkjLBeMKGg</t>
@@ -16104,7 +16168,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/08_云 0.1.4.md</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Byh8rxMFGl</t>
@@ -16147,7 +16215,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/10_云 0.2.6.md</t>
         </is>
       </c>
-      <c r="F20" s="6" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HklvrlGYGg</t>
@@ -16190,7 +16262,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/11_云 0.1.6.md</t>
         </is>
       </c>
-      <c r="F21" s="6" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1MwHgMFMx</t>
@@ -16233,7 +16309,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/12_云 0.1.2.md</t>
         </is>
       </c>
-      <c r="F22" s="6" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1mDrgfKMg</t>
@@ -16276,7 +16356,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/13_云 0.0.1.md</t>
         </is>
       </c>
-      <c r="F23" s="6" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryBPSxGtzg</t>
@@ -16319,7 +16403,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/14_云 0.1.5.md</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BkwPrgGtzg</t>
@@ -16362,7 +16450,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/15_云 0.2.7.md</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJFDrlfKGg</t>
@@ -16405,7 +16497,11 @@
           <t>ORIGINAL/云飛弦/企劃短打/16_云 DIY.md</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/B1UtllnKGg</t>
@@ -16448,7 +16544,11 @@
           <t>ORIGINAL/云飛弦/Others/01_春臨(咪金).md</t>
         </is>
       </c>
-      <c r="F27" s="6" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SkqPBxMKGl</t>
@@ -16491,7 +16591,11 @@
           <t>ORIGINAL/云飛弦/Others/02_暮曙光(歐爾Q).md</t>
         </is>
       </c>
-      <c r="F28" s="6" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryhPHxftGe</t>
@@ -16534,7 +16638,11 @@
           <t>ORIGINAL/云飛弦/Others/03_重逢、涅斯托耳之杯、殘缺的聖歌(云飛弦).md</t>
         </is>
       </c>
-      <c r="F29" s="6" t="n"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1CPBeGtMg</t>
@@ -16577,7 +16685,11 @@
           <t>ORIGINAL/云飛弦/Others/04_提爐香船、漆黑的砂土、圓舞曲(歐爾頓).md</t>
         </is>
       </c>
-      <c r="F30" s="6" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HyxdHxzFfx</t>
@@ -16620,7 +16732,11 @@
           <t>ORIGINAL/云飛弦/Others/05_永生花、忒修斯之船、晨曦(？？？).md</t>
         </is>
       </c>
-      <c r="F31" s="6" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJM_HgzKGg</t>
@@ -16663,7 +16779,11 @@
           <t>ORIGINAL/云飛弦/Others/06_雙人舞、瓦爾普吉斯之夜、水晶杯(咪金).md</t>
         </is>
       </c>
-      <c r="F32" s="6" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SJmuSlGKzx</t>
@@ -16706,7 +16826,11 @@
           <t>ORIGINAL/云飛弦/非企內文章/01_筑云前導.md</t>
         </is>
       </c>
-      <c r="F33" s="6" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1rOBeztzg</t>
@@ -16788,7 +16912,11 @@
           <t>ORIGINAL/范柏舟/柏舟/01_柏舟00.md</t>
         </is>
       </c>
-      <c r="F35" s="6" t="n"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1vD7GGPfl</t>
@@ -16831,7 +16959,11 @@
           <t>ORIGINAL/范柏舟/柏舟/02_柏舟01.md</t>
         </is>
       </c>
-      <c r="F36" s="6" t="n"/>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HyswQGGDzl</t>
@@ -16874,7 +17006,11 @@
           <t>ORIGINAL/范柏舟/柏舟/03_柏舟02.md</t>
         </is>
       </c>
-      <c r="F37" s="6" t="n"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/By0wQfGPGg</t>
@@ -16917,7 +17053,11 @@
           <t>ORIGINAL/范柏舟/關於EX那些事/01_Isaac 01.md</t>
         </is>
       </c>
-      <c r="F38" s="6" t="n"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/B1fOXMfvfe</t>
@@ -16960,7 +17100,11 @@
           <t>ORIGINAL/范柏舟/關於EX那些事/02_Isaac 02.md</t>
         </is>
       </c>
-      <c r="F39" s="6" t="n"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1U_XzGDGe</t>
@@ -17003,7 +17147,11 @@
           <t>ORIGINAL/范柏舟/關於EX那些事/03_Isaac 03.md</t>
         </is>
       </c>
-      <c r="F40" s="6" t="n"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H19dXMGvfe</t>
@@ -17046,7 +17194,11 @@
           <t>ORIGINAL/范柏舟/關於EX那些事/04_Isaac 04.md</t>
         </is>
       </c>
-      <c r="F41" s="6" t="n"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJTumMfvfe</t>
@@ -17089,7 +17241,11 @@
           <t>ORIGINAL/范柏舟/關於EX那些事/05_Isaac 05.md</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1-YQffvMl</t>
@@ -17132,7 +17288,11 @@
           <t>ORIGINAL/范柏舟/關於EX那些事/06_Isaac 06.md</t>
         </is>
       </c>
-      <c r="F43" s="6" t="n"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJHY7Gfvfl</t>
@@ -17214,7 +17374,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/01_Aegir 0.0.0.md</t>
         </is>
       </c>
-      <c r="F45" s="6" t="n"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJjafMGPGl</t>
@@ -17257,7 +17421,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/03_Aegir 1.1.1.md</t>
         </is>
       </c>
-      <c r="F46" s="6" t="n"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkmRfMfwfx</t>
@@ -17300,7 +17468,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/05_Aegir 1.1.2.md</t>
         </is>
       </c>
-      <c r="F47" s="6" t="n"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Byc0MzMDzg</t>
@@ -17343,7 +17515,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/07_Aegir 1.1.3.md</t>
         </is>
       </c>
-      <c r="F48" s="6" t="n"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SkZkXzGwMg</t>
@@ -17386,7 +17562,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/06_Aegir 1.2.1.md</t>
         </is>
       </c>
-      <c r="F49" s="6" t="n"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkC0zfMvzl</t>
@@ -17429,7 +17609,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/04_Aegir 2.4.1.md</t>
         </is>
       </c>
-      <c r="F50" s="6" t="n"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BkUAMzMwMl</t>
@@ -17472,7 +17656,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/02_Aegir 2.6.1.md</t>
         </is>
       </c>
-      <c r="F51" s="6" t="n"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJy0ffGwMl</t>
@@ -17515,7 +17703,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/09_Aegir 4.1.1.md</t>
         </is>
       </c>
-      <c r="F52" s="6" t="n"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkOJQzMDMl</t>
@@ -17558,7 +17750,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/10_Aegir 4.1.2.md</t>
         </is>
       </c>
-      <c r="F53" s="6" t="n"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r12J7fGvze</t>
@@ -17601,7 +17797,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/11_Aegir 4.1.3.md</t>
         </is>
       </c>
-      <c r="F54" s="6" t="n"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BkllQMMPGx</t>
@@ -17644,7 +17844,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/12_Aegir 4.8.1.md</t>
         </is>
       </c>
-      <c r="F55" s="6" t="n"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/ryQlXGMDGx</t>
@@ -17687,7 +17891,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/14_Aegir 5.1.1.md</t>
         </is>
       </c>
-      <c r="F56" s="6" t="n"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Sk9gQffwMx</t>
@@ -17730,7 +17938,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/08_Aegir 5.8.1.md</t>
         </is>
       </c>
-      <c r="F57" s="6" t="n"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/H1rkXGfPfl</t>
@@ -17773,7 +17985,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/13_Aegir 5.8.2.md</t>
         </is>
       </c>
-      <c r="F58" s="6" t="n"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Skwe7zzvMx</t>
@@ -17816,7 +18032,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/15_Aegir 5.8.3.md</t>
         </is>
       </c>
-      <c r="F59" s="6" t="n"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/r1CxQMzPze</t>
@@ -17859,7 +18079,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/16_Plat du jour.md</t>
         </is>
       </c>
-      <c r="F60" s="6" t="n"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rJM-QGzwzl</t>
@@ -17902,7 +18126,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/17_亞格爾與仙人跳.md</t>
         </is>
       </c>
-      <c r="F61" s="6" t="n"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJSW7GfPzl</t>
@@ -17945,7 +18173,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/18_嬌蠻女友.md</t>
         </is>
       </c>
-      <c r="F62" s="6" t="n"/>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HkFb7fMPfg</t>
@@ -17988,7 +18220,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/19_生理反應.md</t>
         </is>
       </c>
-      <c r="F63" s="6" t="n"/>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/By6-XffPze</t>
@@ -18031,7 +18267,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/20_隨筆(亞格爾性轉).md</t>
         </is>
       </c>
-      <c r="F64" s="6" t="n"/>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HkeGXMzDfl</t>
@@ -18074,7 +18314,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/21_自瀉.md</t>
         </is>
       </c>
-      <c r="F65" s="6" t="n"/>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkNzmzMwGx</t>
@@ -18117,7 +18361,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/22_新年舞會.md</t>
         </is>
       </c>
-      <c r="F66" s="6" t="n"/>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HywGQzGvGe</t>
@@ -18160,7 +18408,11 @@
           <t>ORIGINAL/Aegir Marinus/Aegir/23_讀書會.md</t>
         </is>
       </c>
-      <c r="F67" s="6" t="n"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/rkiGmGfPzx</t>
@@ -18203,7 +18455,11 @@
           <t>ORIGINAL/Aegir Marinus/Others(A.M.)/01_Aquatica 1.3.1.md</t>
         </is>
       </c>
-      <c r="F68" s="6" t="n"/>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SykQ7zMvzg</t>
@@ -18246,7 +18502,11 @@
           <t>ORIGINAL/Aegir Marinus/Others(A.M.)/02_Aquatica 2.3.1.md</t>
         </is>
       </c>
-      <c r="F69" s="6" t="n"/>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/SyGm7fMDfg</t>
@@ -18289,7 +18549,11 @@
           <t>ORIGINAL/Aegir Marinus/Others(A.M.)/03_Aquatica 2.3.2.md</t>
         </is>
       </c>
-      <c r="F70" s="6" t="n"/>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/Hk8mQGzDGl</t>
@@ -18332,7 +18596,11 @@
           <t>ORIGINAL/Aegir Marinus/Others(A.M.)/04_Marinus.md</t>
         </is>
       </c>
-      <c r="F71" s="6" t="n"/>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/HJFmQfMPfg</t>
@@ -18350,43 +18618,42 @@
       </c>
     </row>
     <row r="72" ht="14.4" customHeight="1">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>ORIGINAL</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>Aegir Marinus</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>A.M.・黑手黨趴囉</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
-        <is>
-          <t>海洋環境親善維護財團法人基金會</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/05_海洋環境親善維護財團法人基金會.md</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="n"/>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>https://hackmd.io/@Riska0813/Hk67Qfzvzl</t>
-        </is>
-      </c>
-      <c r="H72" s="12" t="inlineStr">
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>黑手黨什麼的有淨灘活動不是正常的嗎？</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/16_黑手黨什麼的有淨灘活動不是正常的嗎.md</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/SJ0phXksMe</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
         <is>
           <t>TU</t>
         </is>
       </c>
-      <c r="I72" s="12" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>ORIGINAL/Aegir Marinus/Others(A.M.)</t>
         </is>
@@ -18410,18 +18677,22 @@
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>隨筆(花晴)</t>
+          <t>海洋環境親善維護財團法人基金會</t>
         </is>
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/06_隨筆(花晴).md</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="n"/>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/05_海洋環境親善維護財團法人基金會.md</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/H1bEXGMPGx</t>
+          <t>https://hackmd.io/@Riska0813/Hk67Qfzvzl</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
@@ -18453,18 +18724,22 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>隨筆(A.M.黑手黨趴囉)</t>
+          <t>隨筆(花晴)</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/07_隨筆(A.M.黑手黨趴囉).md</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="n"/>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/06_隨筆(花晴).md</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/S1E4QfzwMx</t>
+          <t>https://hackmd.io/@Riska0813/H1bEXGMPGx</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr">
@@ -18491,23 +18766,27 @@
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>A.M.・古風趴囉</t>
+          <t>A.M.・黑手黨趴囉</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>隨筆(A.M.古風趴囉)</t>
+          <t>隨筆(A.M.黑手黨趴囉)</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/15_隨筆(A.M.古風趴囉).md</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="n"/>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/07_隨筆(A.M.黑手黨趴囉).md</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/BJb8XfGwfx</t>
+          <t>https://hackmd.io/@Riska0813/S1E4QfzwMx</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr">
@@ -18534,23 +18813,27 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>A.M.・其他</t>
+          <t>A.M.・古風趴囉</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>雜文(CCO)</t>
+          <t>隨筆(A.M.古風趴囉)</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/08_雜文(CCO).md</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="n"/>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/15_隨筆(A.M.古風趴囉).md</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/S1dVXfGvze</t>
+          <t>https://hackmd.io/@Riska0813/BJb8XfGwfx</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
@@ -18582,18 +18865,22 @@
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>雜文(安捷)</t>
+          <t>雜文(CCO)</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/09_雜文(安捷).md</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="n"/>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/08_雜文(CCO).md</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/H12VQffPfl</t>
+          <t>https://hackmd.io/@Riska0813/S1dVXfGvze</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
@@ -18625,18 +18912,22 @@
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>西洋棋的狠心</t>
+          <t>雜文(安捷)</t>
         </is>
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/10_西洋棋的狠心.md</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="n"/>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/09_雜文(安捷).md</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/Hk1SmGGvMe</t>
+          <t>https://hackmd.io/@Riska0813/H12VQffPfl</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
@@ -18668,18 +18959,22 @@
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>結</t>
+          <t>西洋棋的狠心</t>
         </is>
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/11_結.md</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="n"/>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/10_西洋棋的狠心.md</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/BJXBmGMPMe</t>
+          <t>https://hackmd.io/@Riska0813/Hk1SmGGvMe</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
@@ -18711,26 +19006,30 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>囑託</t>
+          <t>結</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/12_囑託.md</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="n"/>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/11_結.md</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/S1PB7zMwfl</t>
-        </is>
-      </c>
-      <c r="H80" s="11" t="inlineStr">
-        <is>
-          <t>Aegir Marinus,TU</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="inlineStr">
+          <t>https://hackmd.io/@Riska0813/BJXBmGMPMe</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="inlineStr">
         <is>
           <t>ORIGINAL/Aegir Marinus/Others(A.M.)</t>
         </is>
@@ -18754,18 +19053,22 @@
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>早安</t>
+          <t>囑託</t>
         </is>
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/13_早安.md</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="n"/>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/12_囑託.md</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/rkcSmGfvGe</t>
+          <t>https://hackmd.io/@Riska0813/S1PB7zMwfl</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
@@ -18797,18 +19100,22 @@
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>後來</t>
+          <t>早安</t>
         </is>
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/14_後來.md</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="n"/>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/13_早安.md</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/BkCSXGzvfx</t>
+          <t>https://hackmd.io/@Riska0813/rkcSmGfvGe</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
@@ -18830,33 +19137,42 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Antey Farr</t>
+          <t>Aegir Marinus</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>A.M.・其他</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Antey Farr｜角色介紹</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>ORIGINAL/Antey Farr/00_Antey Farr｜角色介紹.md</t>
-        </is>
-      </c>
-      <c r="F83" s="6" t="n"/>
+          <t>後來</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)/14_後來.md</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/BkcTbJXPzx</t>
+          <t>https://hackmd.io/@Riska0813/BkCSXGzvfx</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>角色設定,Antey Farr</t>
+          <t>Aegir Marinus,TU</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>ORIGINAL/Antey Farr</t>
+          <t>ORIGINAL/Aegir Marinus/Others(A.M.)</t>
         </is>
       </c>
     </row>
@@ -18871,35 +19187,30 @@
           <t>Antey Farr</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>Antey Farr・Antey</t>
-        </is>
-      </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Antey 00</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
-        <is>
-          <t>ORIGINAL/Antey Farr/Antey/01_Antey 00.md</t>
+          <t>Antey Farr｜角色介紹</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>ORIGINAL/Antey Farr/00_Antey Farr｜角色介紹.md</t>
         </is>
       </c>
       <c r="F84" s="6" t="n"/>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/SyH8QfzvMe</t>
-        </is>
-      </c>
-      <c r="H84" s="12" t="inlineStr">
-        <is>
-          <t>Antey Farr</t>
-        </is>
-      </c>
-      <c r="I84" s="12" t="inlineStr">
-        <is>
-          <t>ORIGINAL/Antey Farr/Antey</t>
+          <t>https://hackmd.io/@Riska0813/BkcTbJXPzx</t>
+        </is>
+      </c>
+      <c r="H84" s="11" t="inlineStr">
+        <is>
+          <t>角色設定,Antey Farr</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>ORIGINAL/Antey Farr</t>
         </is>
       </c>
     </row>
@@ -18921,18 +19232,22 @@
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Antey 01</t>
+          <t>Antey 00</t>
         </is>
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Antey Farr/Antey/02_Antey 01.md</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="n"/>
+          <t>ORIGINAL/Antey Farr/Antey/01_Antey 00.md</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/rJKIQMGPzl</t>
+          <t>https://hackmd.io/@Riska0813/SyH8QfzvMe</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -18959,23 +19274,27 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Antey Farr・隨筆</t>
+          <t>Antey Farr・Antey</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>隨筆 00</t>
+          <t>Antey 01</t>
         </is>
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Antey Farr/Antey/03_隨筆 00.md</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="n"/>
+          <t>ORIGINAL/Antey Farr/Antey/02_Antey 01.md</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/BJ3UXfzwzg</t>
+          <t>https://hackmd.io/@Riska0813/rJKIQMGPzl</t>
         </is>
       </c>
       <c r="H86" s="12" t="inlineStr">
@@ -19007,18 +19326,22 @@
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>隨筆 01</t>
+          <t>隨筆 00</t>
         </is>
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/Antey Farr/Antey/04_隨筆 01.md</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="n"/>
+          <t>ORIGINAL/Antey Farr/Antey/03_隨筆 00.md</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/HyevQzMvGg</t>
+          <t>https://hackmd.io/@Riska0813/BJ3UXfzwzg</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
@@ -19040,38 +19363,42 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>非企劃原創</t>
+          <t>Antey Farr</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>非企劃・顧俞森×斐秀</t>
+          <t>Antey Farr・隨筆</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>補習班</t>
+          <t>隨筆 01</t>
         </is>
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/非企劃原創/01_補習班(顧俞森×斐秀).md</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="n"/>
+          <t>ORIGINAL/Antey Farr/Antey/04_隨筆 01.md</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/ryTYXGMvzg</t>
+          <t>https://hackmd.io/@Riska0813/HyevQzMvGg</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
         <is>
-          <t>非企劃原創,顧俞森,斐秀</t>
+          <t>Antey Farr</t>
         </is>
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>ORIGINAL/非企劃原創</t>
+          <t>ORIGINAL/Antey Farr/Antey</t>
         </is>
       </c>
     </row>
@@ -19093,18 +19420,22 @@
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>告白</t>
+          <t>補習班</t>
         </is>
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/非企劃原創/02_告白(顧俞森×斐秀).md</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="n"/>
+          <t>ORIGINAL/非企劃原創/01_補習班(顧俞森×斐秀).md</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/HJe9QGMvfg</t>
+          <t>https://hackmd.io/@Riska0813/ryTYXGMvzg</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
@@ -19131,28 +19462,32 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>非企劃・帝燣</t>
+          <t>非企劃・顧俞森×斐秀</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>帝燣｜新居日常</t>
+          <t>告白</t>
         </is>
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>ORIGINAL/非企劃原創/02_帝燣｜新居日常.md</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="n"/>
+          <t>ORIGINAL/非企劃原創/02_告白(顧俞森×斐秀).md</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>https://hackmd.io/@Riska0813/rkE9mMGPMe</t>
+          <t>https://hackmd.io/@Riska0813/HJe9QGMvfg</t>
         </is>
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>非企劃原創,帝燣</t>
+          <t>非企劃原創,顧俞森,斐秀</t>
         </is>
       </c>
       <c r="I90" s="12" t="inlineStr">
@@ -19179,35 +19514,81 @@
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
+          <t>帝燣｜新居日常</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>ORIGINAL/非企劃原創/02_帝燣｜新居日常.md</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>https://hackmd.io/@Riska0813/rkE9mMGPMe</t>
+        </is>
+      </c>
+      <c r="H91" s="12" t="inlineStr">
+        <is>
+          <t>非企劃原創,帝燣</t>
+        </is>
+      </c>
+      <c r="I91" s="12" t="inlineStr">
+        <is>
+          <t>ORIGINAL/非企劃原創</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>ORIGINAL</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>非企劃原創</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>非企劃・帝燣</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
           <t>帝燣｜Date</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr">
+      <c r="E92" s="9" t="inlineStr">
         <is>
           <t>ORIGINAL/非企劃原創/01_帝燣｜Date.md</t>
         </is>
       </c>
-      <c r="F91" s="6" t="n"/>
-      <c r="G91" s="9" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>更新</t>
+        </is>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
         <is>
           <t>https://hackmd.io/@Riska0813/BJFKXffwMl</t>
         </is>
       </c>
-      <c r="H91" s="12" t="inlineStr">
+      <c r="H92" s="12" t="inlineStr">
         <is>
           <t>非企劃原創,帝燣</t>
         </is>
       </c>
-      <c r="I91" s="12" t="inlineStr">
+      <c r="I92" s="12" t="inlineStr">
         <is>
           <t>ORIGINAL/非企劃原創</t>
         </is>
       </c>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="F92" s="12" t="n"/>
-      <c r="H92" s="7" t="n"/>
-      <c r="I92" s="7" t="n"/>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="F93" s="12" t="n"/>
@@ -21253,6 +21634,11 @@
       <c r="F501" s="12" t="n"/>
       <c r="H501" s="7" t="n"/>
       <c r="I501" s="7" t="n"/>
+    </row>
+    <row r="502">
+      <c r="F502" s="12" t="n"/>
+      <c r="H502" s="7" t="n"/>
+      <c r="I502" s="7" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
